--- a/public/downloads/FloresActive2020.xlsx
+++ b/public/downloads/FloresActive2020.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -659,10 +682,10 @@
         <v>96</v>
       </c>
       <c r="N3" s="5">
-        <v>951.1594116687775</v>
+        <v>951159.4116687775</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03387440477469915</v>
+        <v>33.87440477469915</v>
       </c>
       <c r="P3" s="5">
         <v>28079</v>
@@ -709,10 +732,10 @@
         <v>96</v>
       </c>
       <c r="N4" s="5">
-        <v>1538.092978000641</v>
+        <v>1538092.978000641</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06636862903994135</v>
+        <v>66.36862903994135</v>
       </c>
       <c r="P4" s="5">
         <v>23175</v>
@@ -759,10 +782,10 @@
         <v>96</v>
       </c>
       <c r="N5" s="5">
-        <v>2011.067974328995</v>
+        <v>2011067.974328995</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1317005877098228</v>
+        <v>131.7005877098229</v>
       </c>
       <c r="P5" s="5">
         <v>15270</v>
@@ -809,10 +832,10 @@
         <v>96</v>
       </c>
       <c r="N6" s="5">
-        <v>2367.700353622437</v>
+        <v>2367700.353622437</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08926633817005114</v>
+        <v>89.26633817005114</v>
       </c>
       <c r="P6" s="5">
         <v>26524</v>
@@ -859,10 +882,10 @@
         <v>96</v>
       </c>
       <c r="N7" s="5">
-        <v>3305.167227506638</v>
+        <v>3305167.227506638</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2954735586900266</v>
+        <v>295.4735586900266</v>
       </c>
       <c r="P7" s="5">
         <v>11186</v>
@@ -909,10 +932,10 @@
         <v>96</v>
       </c>
       <c r="N8" s="5">
-        <v>416.7273724079132</v>
+        <v>416727.3724079132</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01973234397499471</v>
+        <v>19.73234397499471</v>
       </c>
       <c r="P8" s="5">
         <v>21119</v>
@@ -959,10 +982,10 @@
         <v>96</v>
       </c>
       <c r="N9" s="5">
-        <v>929.569278717041</v>
+        <v>929569.278717041</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03352336105582751</v>
+        <v>33.52336105582751</v>
       </c>
       <c r="P9" s="5">
         <v>27729</v>
@@ -1009,10 +1032,10 @@
         <v>96</v>
       </c>
       <c r="N10" s="5">
-        <v>1445.554861783981</v>
+        <v>1445554.861783981</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08713410860662937</v>
+        <v>87.13410860662937</v>
       </c>
       <c r="P10" s="5">
         <v>16590</v>
@@ -1059,10 +1082,10 @@
         <v>96</v>
       </c>
       <c r="N11" s="5">
-        <v>932.6601378917694</v>
+        <v>932660.1378917694</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04345432315574568</v>
+        <v>43.45432315574568</v>
       </c>
       <c r="P11" s="5">
         <v>21463</v>
@@ -1109,10 +1132,10 @@
         <v>96</v>
       </c>
       <c r="N12" s="5">
-        <v>382.6644694805145</v>
+        <v>382664.4694805145</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0220925159910233</v>
+        <v>22.0925159910233</v>
       </c>
       <c r="P12" s="5">
         <v>17321</v>
@@ -1159,10 +1182,10 @@
         <v>96</v>
       </c>
       <c r="N13" s="5">
-        <v>1278.479053735733</v>
+        <v>1278479.053735733</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07707252554471504</v>
+        <v>77.07252554471503</v>
       </c>
       <c r="P13" s="5">
         <v>16588</v>
@@ -1209,10 +1232,10 @@
         <v>96</v>
       </c>
       <c r="N14" s="5">
-        <v>6337.018850326538</v>
+        <v>6337018.850326538</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3970811987171213</v>
+        <v>397.0811987171213</v>
       </c>
       <c r="P14" s="5">
         <v>15959</v>
@@ -1259,10 +1282,10 @@
         <v>96</v>
       </c>
       <c r="N15" s="5">
-        <v>4483.697550058365</v>
+        <v>4483697.550058365</v>
       </c>
       <c r="O15" s="4">
-        <v>0.4166230765711174</v>
+        <v>416.6230765711173</v>
       </c>
       <c r="P15" s="5">
         <v>10762</v>
@@ -1309,10 +1332,10 @@
         <v>96</v>
       </c>
       <c r="N16" s="5">
-        <v>4783.621640920639</v>
+        <v>4783621.640920639</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09992525152324196</v>
+        <v>99.92525152324195</v>
       </c>
       <c r="P16" s="5">
         <v>47872</v>
@@ -1359,10 +1382,10 @@
         <v>96</v>
       </c>
       <c r="N17" s="5">
-        <v>1224.156541347504</v>
+        <v>1224156.541347504</v>
       </c>
       <c r="O17" s="4">
-        <v>0.101564468708828</v>
+        <v>101.564468708828</v>
       </c>
       <c r="P17" s="5">
         <v>12053</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1369960256611082</v>
+        <v>0.1867457055972445</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1266749866906713</v>
+        <v>0.1576969009362092</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1401462838018232</v>
+        <v>0.141375231288175</v>
       </c>
       <c r="E3" s="4">
-        <v>89.89158163265306</v>
+        <v>87.13010204081633</v>
       </c>
       <c r="F3" s="4">
-        <v>88.34941275167785</v>
+        <v>80.06711409395973</v>
       </c>
       <c r="G3" s="5">
         <v>32</v>
       </c>
       <c r="H3" s="5">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1084329173742126</v>
+      </c>
+      <c r="O3" s="5">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1873842471907199</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.163449317763046</v>
+      </c>
+      <c r="R3" s="5">
+        <v>24</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1252639277764069</v>
+        <v>0.1555590689175176</v>
       </c>
       <c r="C4" s="4">
-        <v>0.0866689303581054</v>
+        <v>0.1686865839760918</v>
       </c>
       <c r="D4" s="4">
-        <v>0.08867469798686882</v>
+        <v>0.1909914399592415</v>
       </c>
       <c r="E4" s="4">
-        <v>87.43941326530613</v>
+        <v>84.40688775510205</v>
       </c>
       <c r="F4" s="4">
-        <v>82.46819071588368</v>
+        <v>72.47273489932886</v>
       </c>
       <c r="G4" s="5">
         <v>32</v>
       </c>
       <c r="H4" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1139907354166388</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1358347447442895</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1313027635058236</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2992923205209463</v>
+        <v>0.3201759959009612</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1453087527798594</v>
+        <v>0.3866626022643647</v>
       </c>
       <c r="D5" s="4">
-        <v>0.142873013434469</v>
+        <v>0.5109692009049227</v>
       </c>
       <c r="E5" s="4">
-        <v>83.04528061224521</v>
+        <v>78.67028061224489</v>
       </c>
       <c r="F5" s="4">
-        <v>64.69938478747201</v>
+        <v>53.89890939597316</v>
       </c>
       <c r="G5" s="5">
         <v>32</v>
       </c>
       <c r="H5" s="5">
+        <v>8</v>
+      </c>
+      <c r="I5" s="5">
+        <v>14</v>
+      </c>
+      <c r="J5" s="5">
         <v>10</v>
       </c>
-      <c r="I5" s="5">
-        <v>16</v>
-      </c>
-      <c r="J5" s="5">
-        <v>6</v>
-      </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3866626022643647</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.422702074002875</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.189695373273117</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,66 +1797,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1876340676788395</v>
+        <v>0.9036444197497424</v>
       </c>
       <c r="C3" s="4">
-        <v>0.18661350902889</v>
+        <v>0.9812959807993231</v>
       </c>
       <c r="D3" s="4">
-        <v>0.221086513544325</v>
+        <v>0.9136791258381542</v>
       </c>
       <c r="E3" s="4">
-        <v>86.87712585034014</v>
+        <v>75.84396258503402</v>
       </c>
       <c r="F3" s="4">
-        <v>81.03013143176733</v>
+        <v>75.22930648769581</v>
       </c>
       <c r="G3" s="5">
         <v>32</v>
       </c>
       <c r="H3" s="5">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.9812959807993231</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2397215958098913</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1998112677208215</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1200436261645592</v>
+        <v>0.4847837444817884</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1028032739687546</v>
+        <v>0.5408934887449789</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1097033401020795</v>
+        <v>0.4863735195672376</v>
       </c>
       <c r="E4" s="4">
-        <v>82.88371598639456</v>
+        <v>76.50403911564662</v>
       </c>
       <c r="F4" s="4">
-        <v>72.05641778523488</v>
+        <v>72.51503076062546</v>
       </c>
       <c r="G4" s="5">
         <v>32</v>
@@ -1741,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>12</v>
+      </c>
+      <c r="K4" s="5">
         <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>10</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>10</v>
@@ -1755,40 +1915,58 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.5408934887449789</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2083847138374097</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2228164212460968</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.507916872530533</v>
+        <v>0.9334257724267836</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4580083439673217</v>
+        <v>0.9909065687482013</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3451731474133304</v>
+        <v>0.8087549478741458</v>
       </c>
       <c r="E5" s="4">
-        <v>76.09481292517</v>
+        <v>65.35182823129239</v>
       </c>
       <c r="F5" s="4">
-        <v>53.14772091722593</v>
+        <v>55.46071029082763</v>
       </c>
       <c r="G5" s="5">
         <v>32</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J5" s="5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5" s="5">
         <v>12</v>
@@ -1796,9 +1974,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.9909065687482013</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.263456585764194</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09053968377930488</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,81 +2097,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1526654651358008</v>
+        <v>0.1369960256611082</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1266532503511005</v>
+        <v>0.1266749866906713</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1263495166857886</v>
+        <v>0.1401462838018232</v>
       </c>
       <c r="E3" s="4">
-        <v>90.36670918367346</v>
+        <v>89.89158163265306</v>
       </c>
       <c r="F3" s="4">
-        <v>86.89911912751715</v>
+        <v>88.34941275167785</v>
       </c>
       <c r="G3" s="5">
         <v>32</v>
       </c>
       <c r="H3" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01823851120300507</v>
+      </c>
+      <c r="O3" s="5">
+        <v>30</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1432850208500692</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.13459914897243</v>
+      </c>
+      <c r="R3" s="5">
+        <v>30</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1326882222613719</v>
+        <v>0.1252639277764069</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1039080218015143</v>
+        <v>0.0866689303581054</v>
       </c>
       <c r="D4" s="4">
-        <v>0.09100556273072158</v>
+        <v>0.08867469798686882</v>
       </c>
       <c r="E4" s="4">
-        <v>88.31207482993197</v>
+        <v>87.43941326530613</v>
       </c>
       <c r="F4" s="4">
-        <v>79.65429250559414</v>
+        <v>82.46819071588368</v>
       </c>
       <c r="G4" s="5">
         <v>32</v>
       </c>
       <c r="H4" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>4</v>
@@ -1968,50 +2215,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.01718687351574845</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1234749091836523</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09001253007301536</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5011637535920812</v>
+        <v>0.2992923205209463</v>
       </c>
       <c r="C5" s="4">
-        <v>0.09535758483156087</v>
+        <v>0.1453087527798594</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1228187637628331</v>
+        <v>0.142873013434469</v>
       </c>
       <c r="E5" s="4">
-        <v>81.8431122448979</v>
+        <v>83.04528061224521</v>
       </c>
       <c r="F5" s="4">
-        <v>59.29565156599624</v>
+        <v>64.69938478747201</v>
       </c>
       <c r="G5" s="5">
         <v>32</v>
       </c>
       <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="5">
+        <v>16</v>
+      </c>
+      <c r="J5" s="5">
         <v>6</v>
       </c>
-      <c r="I5" s="5">
-        <v>14</v>
-      </c>
-      <c r="J5" s="5">
-        <v>12</v>
-      </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.1453087527798594</v>
+      </c>
+      <c r="O5" s="5">
         <v>10</v>
       </c>
-      <c r="M5" s="5">
+      <c r="P5" s="4">
+        <v>0.3650256626391886</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09409969255448772</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,25 +2397,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1120615823162971</v>
+        <v>0.1876340676788395</v>
       </c>
       <c r="C3" s="4">
-        <v>0.0843890894927575</v>
+        <v>0.18661350902889</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1287542719378827</v>
+        <v>0.221086513544325</v>
       </c>
       <c r="E3" s="4">
-        <v>89.16454081632654</v>
+        <v>86.87712585034014</v>
       </c>
       <c r="F3" s="4">
-        <v>88.57802013422818</v>
+        <v>81.03013143176733</v>
       </c>
       <c r="G3" s="5">
         <v>32</v>
@@ -2140,25 +2456,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1361825174318221</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.179968819332004</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1496413203134285</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2707845214331286</v>
+        <v>0.1200436261645592</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2063922611655414</v>
+        <v>0.1028032739687546</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2275451663458483</v>
+        <v>0.1097033401020795</v>
       </c>
       <c r="E4" s="4">
-        <v>86.39455782312926</v>
+        <v>82.88371598639456</v>
       </c>
       <c r="F4" s="4">
-        <v>80.54565156599539</v>
+        <v>72.05641778523488</v>
       </c>
       <c r="G4" s="5">
         <v>32</v>
@@ -2167,64 +2501,100 @@
         <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.02073810971091916</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1226358898784241</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1028032739687546</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4778377152679489</v>
+        <v>0.507916872530533</v>
       </c>
       <c r="C5" s="4">
-        <v>0.04876166047166634</v>
+        <v>0.4580083439673217</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1674662269352005</v>
+        <v>0.3451731474133304</v>
       </c>
       <c r="E5" s="4">
-        <v>83.13350340136056</v>
+        <v>76.09481292517</v>
       </c>
       <c r="F5" s="4">
-        <v>64.59032438478746</v>
+        <v>53.14772091722593</v>
       </c>
       <c r="G5" s="5">
         <v>32</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4580083439673217</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8034131196704486</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08051013341147002</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.369491259110693</v>
+        <v>0.1526654651358008</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3729601556301379</v>
+        <v>0.1266532503511005</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3664579788544088</v>
+        <v>0.1263495166857886</v>
       </c>
       <c r="E3" s="4">
-        <v>80.84821428571429</v>
+        <v>90.36670918367346</v>
       </c>
       <c r="F3" s="4">
-        <v>83.29872762863533</v>
+        <v>86.89911912751715</v>
       </c>
       <c r="G3" s="5">
         <v>32</v>
       </c>
       <c r="H3" s="5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.006114199231869104</v>
+      </c>
+      <c r="O3" s="5">
+        <v>27</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1534297400397844</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1282384131149184</v>
+      </c>
+      <c r="R3" s="5">
+        <v>27</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1687713067354022</v>
+        <v>0.1326882222613719</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1789393367317205</v>
+        <v>0.1039080218015143</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1897489515091515</v>
+        <v>0.09100556273072158</v>
       </c>
       <c r="E4" s="4">
-        <v>80.89710884353741</v>
+        <v>88.31207482993197</v>
       </c>
       <c r="F4" s="4">
-        <v>81.49154082774059</v>
+        <v>79.65429250559414</v>
       </c>
       <c r="G4" s="5">
         <v>32</v>
       </c>
       <c r="H4" s="5">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.09143967352438147</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08712304540424848</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06352271159842908</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3456514664567173</v>
+        <v>0.5011637535920812</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3063374167557849</v>
+        <v>0.09535758483156087</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3540344562143054</v>
+        <v>0.1228187637628331</v>
       </c>
       <c r="E5" s="4">
-        <v>79.49085884353742</v>
+        <v>81.8431122448979</v>
       </c>
       <c r="F5" s="4">
-        <v>77.49335850111845</v>
+        <v>59.29565156599624</v>
       </c>
       <c r="G5" s="5">
         <v>32</v>
       </c>
       <c r="H5" s="5">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J5" s="5">
+        <v>12</v>
+      </c>
+      <c r="K5" s="5">
         <v>2</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.07680233613528269</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5539653596850881</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06975680611979997</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2997,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2189796616665428</v>
+        <v>0.1120615823162971</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2324897232166832</v>
+        <v>0.0843890894927575</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2408469702728383</v>
+        <v>0.1287542719378827</v>
       </c>
       <c r="E3" s="4">
-        <v>95.25510204081633</v>
+        <v>89.16454081632654</v>
       </c>
       <c r="F3" s="4">
-        <v>93.09249161073828</v>
+        <v>88.57802013422818</v>
       </c>
       <c r="G3" s="5">
         <v>32</v>
       </c>
       <c r="H3" s="5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.04745056970985546</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1026831647686435</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08379655321330427</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3568956075891938</v>
+        <v>0.2707845214331286</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3463653981747571</v>
+        <v>0.2063922611655414</v>
       </c>
       <c r="D4" s="4">
-        <v>0.354755902620526</v>
+        <v>0.2275451663458483</v>
       </c>
       <c r="E4" s="4">
-        <v>94.90327380952381</v>
+        <v>86.39455782312926</v>
       </c>
       <c r="F4" s="4">
-        <v>91.69358221476512</v>
+        <v>80.54565156599539</v>
       </c>
       <c r="G4" s="5">
         <v>32</v>
       </c>
       <c r="H4" s="5">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2063922611655414</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1342232975488358</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08784778205000976</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5821395191369274</v>
+        <v>0.4778377152679489</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4983092251751334</v>
+        <v>0.04876166047166634</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5114960401324837</v>
+        <v>0.1674662269352005</v>
       </c>
       <c r="E5" s="4">
-        <v>92.46279761904762</v>
+        <v>83.13350340136056</v>
       </c>
       <c r="F5" s="4">
-        <v>81.45693512304261</v>
+        <v>64.59032438478746</v>
       </c>
       <c r="G5" s="5">
         <v>32</v>
       </c>
       <c r="H5" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5">
+        <v>14</v>
+      </c>
+      <c r="J5" s="5">
+        <v>8</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>8</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.03691797655172877</v>
+      </c>
+      <c r="O5" s="5">
         <v>10</v>
       </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="P5" s="4">
+        <v>0.4509789854492503</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04403327346563402</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3297,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7754225428567214</v>
+        <v>0.369491259110693</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5787497327404897</v>
+        <v>0.3729601556301379</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7087313509634728</v>
+        <v>0.3664579788544088</v>
       </c>
       <c r="E3" s="4">
-        <v>59.70875850340139</v>
+        <v>80.84821428571429</v>
       </c>
       <c r="F3" s="4">
-        <v>56.97357382550308</v>
+        <v>83.29872762863533</v>
       </c>
       <c r="G3" s="5">
         <v>32</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3729601556301379</v>
+      </c>
+      <c r="O3" s="5">
+        <v>30</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07972252781469347</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08133720671493162</v>
+      </c>
+      <c r="R3" s="5">
+        <v>30</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7778374829246173</v>
+        <v>0.1687713067354022</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5542227504002055</v>
+        <v>0.1789393367317205</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6457280647433425</v>
+        <v>0.1897489515091515</v>
       </c>
       <c r="E4" s="4">
-        <v>61.41369047619047</v>
+        <v>80.89710884353741</v>
       </c>
       <c r="F4" s="4">
-        <v>57.491261185682</v>
+        <v>81.49154082774059</v>
       </c>
       <c r="G4" s="5">
         <v>32</v>
       </c>
       <c r="H4" s="5">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1789393367317205</v>
+      </c>
+      <c r="O4" s="5">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05820572572333539</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05261639683380094</v>
+      </c>
+      <c r="R4" s="5">
+        <v>28</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.807282285053092</v>
+        <v>0.3456514664567173</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6809700602118953</v>
+        <v>0.3063374167557849</v>
       </c>
       <c r="D5" s="4">
-        <v>0.8046411284240977</v>
+        <v>0.3540344562143054</v>
       </c>
       <c r="E5" s="4">
-        <v>58.30250850340131</v>
+        <v>79.49085884353742</v>
       </c>
       <c r="F5" s="4">
-        <v>52.38359899328869</v>
+        <v>77.49335850111845</v>
       </c>
       <c r="G5" s="5">
         <v>32</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
         <v>2</v>
       </c>
-      <c r="L5" s="5">
-        <v>18</v>
-      </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3063374167557849</v>
+      </c>
+      <c r="O5" s="5">
+        <v>25</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1434354921257837</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06381629813735254</v>
+      </c>
+      <c r="R5" s="5">
+        <v>25</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,25 +3597,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1627205844647709</v>
+        <v>0.2189796616665428</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1560968441278688</v>
+        <v>0.2324897232166832</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1629680033452371</v>
+        <v>0.2408469702728383</v>
       </c>
       <c r="E3" s="4">
-        <v>93.33971088435375</v>
+        <v>95.25510204081633</v>
       </c>
       <c r="F3" s="4">
-        <v>91.10773210290826</v>
+        <v>93.09249161073828</v>
       </c>
       <c r="G3" s="5">
         <v>32</v>
@@ -2992,25 +3656,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2274285967907106</v>
+      </c>
+      <c r="O3" s="5">
+        <v>30</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07942627253031928</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06847086835199741</v>
+      </c>
+      <c r="R3" s="5">
+        <v>30</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2526627024212822</v>
+        <v>0.3568956075891938</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2097424409488105</v>
+        <v>0.3463653981747571</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2060347242099094</v>
+        <v>0.354755902620526</v>
       </c>
       <c r="E4" s="4">
-        <v>91.62096088435374</v>
+        <v>94.90327380952381</v>
       </c>
       <c r="F4" s="4">
-        <v>86.59116331096197</v>
+        <v>91.69358221476512</v>
       </c>
       <c r="G4" s="5">
         <v>32</v>
@@ -3033,34 +3715,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3463653981747571</v>
+      </c>
+      <c r="O4" s="5">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1069591392740156</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06072372010026771</v>
+      </c>
+      <c r="R4" s="5">
+        <v>28</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2662898544743428</v>
+        <v>0.5821395191369274</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2362086074525696</v>
+        <v>0.4983092251751334</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2306268428543539</v>
+        <v>0.5114960401324837</v>
       </c>
       <c r="E5" s="4">
-        <v>91.05548469387755</v>
+        <v>92.46279761904762</v>
       </c>
       <c r="F5" s="4">
-        <v>80.43029921700217</v>
+        <v>81.45693512304261</v>
       </c>
       <c r="G5" s="5">
         <v>32</v>
       </c>
       <c r="H5" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5" s="5">
         <v>2</v>
@@ -3074,9 +3774,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.4983092251751334</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1607667576311123</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0982460521811285</v>
+      </c>
+      <c r="R5" s="5">
+        <v>20</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7754225428567214</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5787497327404897</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7087313509634728</v>
+      </c>
+      <c r="E3" s="4">
+        <v>59.70875850340139</v>
+      </c>
+      <c r="F3" s="4">
+        <v>56.97357382550308</v>
+      </c>
+      <c r="G3" s="5">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>20</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>17</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.5787497327404897</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4654902201714125</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0388690767543188</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.7778374829246173</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5542227504002055</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6457280647433425</v>
+      </c>
+      <c r="E4" s="4">
+        <v>61.41369047619047</v>
+      </c>
+      <c r="F4" s="4">
+        <v>57.491261185682</v>
+      </c>
+      <c r="G4" s="5">
+        <v>32</v>
+      </c>
+      <c r="H4" s="5">
+        <v>14</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>18</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
+        <v>15</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.5542227504002055</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4147755202636663</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05900197025465533</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.807282285053092</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6809700602118953</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.8046411284240977</v>
+      </c>
+      <c r="E5" s="4">
+        <v>58.30250850340131</v>
+      </c>
+      <c r="F5" s="4">
+        <v>52.38359899328869</v>
+      </c>
+      <c r="G5" s="5">
+        <v>32</v>
+      </c>
+      <c r="H5" s="5">
+        <v>8</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>18</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.6809700602118953</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3426818305383996</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05365115684207922</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1627205844647709</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1560968441278688</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1629680033452371</v>
+      </c>
+      <c r="E3" s="4">
+        <v>93.33971088435375</v>
+      </c>
+      <c r="F3" s="4">
+        <v>91.10773210290826</v>
+      </c>
+      <c r="G3" s="5">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5">
+        <v>30</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1388296321789266</v>
+      </c>
+      <c r="O3" s="5">
+        <v>30</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07306235924582898</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0697167127062592</v>
+      </c>
+      <c r="R3" s="5">
+        <v>30</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2526627024212822</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2097424409488105</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2060347242099094</v>
+      </c>
+      <c r="E4" s="4">
+        <v>91.62096088435374</v>
+      </c>
+      <c r="F4" s="4">
+        <v>86.59116331096197</v>
+      </c>
+      <c r="G4" s="5">
+        <v>32</v>
+      </c>
+      <c r="H4" s="5">
+        <v>28</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2097424409488105</v>
+      </c>
+      <c r="O4" s="5">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1059114007419001</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07198987345077534</v>
+      </c>
+      <c r="R4" s="5">
+        <v>28</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2662898544743428</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2362086074525696</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2306268428543539</v>
+      </c>
+      <c r="E5" s="4">
+        <v>91.05548469387755</v>
+      </c>
+      <c r="F5" s="4">
+        <v>80.43029921700217</v>
+      </c>
+      <c r="G5" s="5">
+        <v>32</v>
+      </c>
+      <c r="H5" s="5">
+        <v>24</v>
+      </c>
+      <c r="I5" s="5">
+        <v>6</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.235324439839441</v>
+      </c>
+      <c r="O5" s="5">
+        <v>24</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1312519382474235</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.095378792456584</v>
+      </c>
+      <c r="R5" s="5">
+        <v>24</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>51.04166666666666</v>
+      </c>
+      <c r="C3" s="3">
+        <v>13.54166666666667</v>
+      </c>
+      <c r="D3" s="3">
+        <v>35.41666666666667</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="F3" s="3">
+        <v>32.29166666666667</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3142599252734728</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1101761418747389</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1458403697112343</v>
+      </c>
+      <c r="K3" s="4">
+        <v>73.04315476190501</v>
+      </c>
+      <c r="L3" s="4">
+        <v>59.70206469052956</v>
+      </c>
+      <c r="M3" s="5">
+        <v>96</v>
+      </c>
+      <c r="N3" s="5">
+        <v>951159.4116687775</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.87440477469915</v>
+      </c>
+      <c r="P3" s="5">
+        <v>28079</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="D4" s="3">
+        <v>31.25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5.208333333333334</v>
+      </c>
+      <c r="F4" s="3">
+        <v>26.04166666666667</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3174461747744334</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.133146481324683</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2385444603736701</v>
+      </c>
+      <c r="K4" s="4">
+        <v>81.85515873015865</v>
+      </c>
+      <c r="L4" s="4">
+        <v>68.48329138702432</v>
+      </c>
+      <c r="M4" s="5">
+        <v>96</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1538092.978000641</v>
+      </c>
+      <c r="O4" s="4">
+        <v>66.36862903994135</v>
+      </c>
+      <c r="P4" s="5">
+        <v>23175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D5" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1135350441598052</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.08699927366929083</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1229860506044749</v>
+      </c>
+      <c r="K5" s="4">
+        <v>85.26856575963723</v>
+      </c>
+      <c r="L5" s="4">
+        <v>81.8854865771826</v>
+      </c>
+      <c r="M5" s="5">
+        <v>96</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2011067.974328995</v>
+      </c>
+      <c r="O5" s="4">
+        <v>131.7005877098229</v>
+      </c>
+      <c r="P5" s="5">
+        <v>15270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45.83333333333333</v>
+      </c>
+      <c r="C6" s="3">
+        <v>14.58333333333333</v>
+      </c>
+      <c r="D6" s="3">
+        <v>39.58333333333333</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>39.58333333333333</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4347210496207794</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2150951707058</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2683755726456744</v>
+      </c>
+      <c r="K6" s="4">
+        <v>69.90610827664401</v>
+      </c>
+      <c r="L6" s="4">
+        <v>65.49787938105885</v>
+      </c>
+      <c r="M6" s="5">
+        <v>96</v>
+      </c>
+      <c r="N6" s="5">
+        <v>2367700.353622437</v>
+      </c>
+      <c r="O6" s="4">
+        <v>89.26633817005114</v>
+      </c>
+      <c r="P6" s="5">
+        <v>26524</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C7" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1020591602119626</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.07128844365397333</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.07299705688779545</v>
+      </c>
+      <c r="K7" s="4">
+        <v>92.96343537414968</v>
+      </c>
+      <c r="L7" s="4">
+        <v>88.04145693512302</v>
+      </c>
+      <c r="M7" s="5">
+        <v>96</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3305167.227506638</v>
+      </c>
+      <c r="O7" s="4">
+        <v>295.4735586900266</v>
+      </c>
+      <c r="P7" s="5">
+        <v>11186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>54.16666666666666</v>
+      </c>
+      <c r="C8" s="3">
+        <v>22.91666666666666</v>
+      </c>
+      <c r="D8" s="3">
+        <v>22.91666666666666</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>22.91666666666666</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2486403553126282</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1551231131272022</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1737207949261137</v>
+      </c>
+      <c r="K8" s="4">
+        <v>83.40242346938747</v>
+      </c>
+      <c r="L8" s="4">
+        <v>68.81291946308666</v>
+      </c>
+      <c r="M8" s="5">
+        <v>96</v>
+      </c>
+      <c r="N8" s="5">
+        <v>416727.3724079132</v>
+      </c>
+      <c r="O8" s="4">
+        <v>19.73234397499471</v>
+      </c>
+      <c r="P8" s="5">
+        <v>21119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>52.08333333333334</v>
+      </c>
+      <c r="C9" s="3">
+        <v>7.291666666666667</v>
+      </c>
+      <c r="D9" s="3">
+        <v>40.625</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7.291666666666667</v>
+      </c>
+      <c r="F9" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.570520965137165</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.191529875700289</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2239449648504734</v>
+      </c>
+      <c r="K9" s="4">
+        <v>72.56660997732412</v>
+      </c>
+      <c r="L9" s="4">
+        <v>67.73501584638278</v>
+      </c>
+      <c r="M9" s="5">
+        <v>96</v>
+      </c>
+      <c r="N9" s="5">
+        <v>929569.278717041</v>
+      </c>
+      <c r="O9" s="4">
+        <v>33.52336105582751</v>
+      </c>
+      <c r="P9" s="5">
+        <v>27729</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C10" s="3">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="D10" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2105951975576367</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1115511268198461</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1148728350544145</v>
+      </c>
+      <c r="K10" s="4">
+        <v>86.79209183673511</v>
+      </c>
+      <c r="L10" s="4">
+        <v>78.50566275167803</v>
+      </c>
+      <c r="M10" s="5">
+        <v>96</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1445554.861783981</v>
+      </c>
+      <c r="O10" s="4">
+        <v>87.13410860662937</v>
+      </c>
+      <c r="P10" s="5">
+        <v>16590</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>54.16666666666666</v>
+      </c>
+      <c r="C11" s="3">
+        <v>15.625</v>
+      </c>
+      <c r="D11" s="3">
+        <v>30.20833333333333</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="F11" s="3">
+        <v>29.16666666666667</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.368672609626959</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1236500116921741</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1683231453380716</v>
+      </c>
+      <c r="K11" s="4">
+        <v>81.95188492063491</v>
+      </c>
+      <c r="L11" s="4">
+        <v>68.74475671140929</v>
+      </c>
+      <c r="M11" s="5">
+        <v>96</v>
+      </c>
+      <c r="N11" s="5">
+        <v>932660.1378917694</v>
+      </c>
+      <c r="O11" s="4">
+        <v>43.45432315574568</v>
+      </c>
+      <c r="P11" s="5">
+        <v>21463</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>54.16666666666666</v>
+      </c>
+      <c r="C12" s="3">
+        <v>22.91666666666666</v>
+      </c>
+      <c r="D12" s="3">
+        <v>22.91666666666666</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="F12" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.264839381709707</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.09784441367676439</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1185811307631417</v>
+      </c>
+      <c r="K12" s="4">
+        <v>86.84063208616764</v>
+      </c>
+      <c r="L12" s="4">
+        <v>75.28302106636806</v>
+      </c>
+      <c r="M12" s="5">
+        <v>96</v>
+      </c>
+      <c r="N12" s="5">
+        <v>382664.4694805145</v>
+      </c>
+      <c r="O12" s="4">
+        <v>22.0925159910233</v>
+      </c>
+      <c r="P12" s="5">
+        <v>17321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="C13" s="3">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="D13" s="3">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>20.83333333333334</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2292951492555766</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.07814283498575796</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1108401261971524</v>
+      </c>
+      <c r="K13" s="4">
+        <v>86.23086734693865</v>
+      </c>
+      <c r="L13" s="4">
+        <v>77.90466536166907</v>
+      </c>
+      <c r="M13" s="5">
+        <v>96</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1278479.053735733</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.07252554471503</v>
+      </c>
+      <c r="P13" s="5">
+        <v>16588</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>86.45833333333334</v>
+      </c>
+      <c r="C14" s="3">
+        <v>7.291666666666667</v>
+      </c>
+      <c r="D14" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.09378791522127085</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.06637087670154446</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.07923886178575115</v>
+      </c>
+      <c r="K14" s="4">
+        <v>80.41206065759638</v>
+      </c>
+      <c r="L14" s="4">
+        <v>80.76120898583056</v>
+      </c>
+      <c r="M14" s="5">
+        <v>96</v>
+      </c>
+      <c r="N14" s="5">
+        <v>6337018.850326538</v>
+      </c>
+      <c r="O14" s="4">
+        <v>397.0811987171213</v>
+      </c>
+      <c r="P14" s="5">
+        <v>15959</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>81.25</v>
+      </c>
+      <c r="C15" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D15" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1157173898118157</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.07332450329474344</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.07696705991267039</v>
+      </c>
+      <c r="K15" s="4">
+        <v>94.20705782312923</v>
+      </c>
+      <c r="L15" s="4">
+        <v>88.74766964951716</v>
+      </c>
+      <c r="M15" s="5">
+        <v>96</v>
+      </c>
+      <c r="N15" s="5">
+        <v>4483697.550058365</v>
+      </c>
+      <c r="O15" s="4">
+        <v>416.6230765711173</v>
+      </c>
+      <c r="P15" s="5">
+        <v>10762</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>35.41666666666667</v>
+      </c>
+      <c r="C16" s="3">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="D16" s="3">
+        <v>60.41666666666666</v>
+      </c>
+      <c r="E16" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="F16" s="3">
+        <v>52.08333333333334</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4076491903244928</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.05063722821628335</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1411355123080472</v>
+      </c>
+      <c r="K16" s="4">
+        <v>59.80831916099748</v>
+      </c>
+      <c r="L16" s="4">
+        <v>55.61614466815848</v>
+      </c>
+      <c r="M16" s="5">
+        <v>96</v>
+      </c>
+      <c r="N16" s="5">
+        <v>4783621.640920639</v>
+      </c>
+      <c r="O16" s="4">
+        <v>99.92525152324195</v>
+      </c>
+      <c r="P16" s="5">
+        <v>47872</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>85.41666666666666</v>
+      </c>
+      <c r="C17" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D17" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1034085660783842</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.07800376654594514</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.08507786156237755</v>
+      </c>
+      <c r="K17" s="4">
+        <v>92.00538548752832</v>
+      </c>
+      <c r="L17" s="4">
+        <v>86.04306487695897</v>
+      </c>
+      <c r="M17" s="5">
+        <v>96</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1224156.541347504</v>
+      </c>
+      <c r="O17" s="4">
+        <v>101.564468708828</v>
+      </c>
+      <c r="P17" s="5">
+        <v>12053</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3209,13 +5385,13 @@
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3259,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3473,13 +5649,13 @@
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3611,7 +5787,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3778,16 +5954,16 @@
         <v>3</v>
       </c>
       <c r="K16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>49</v>
+      </c>
+      <c r="C3" s="5">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5">
+        <v>34</v>
+      </c>
+      <c r="E3" s="5">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5">
+        <v>31</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>20</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>48</v>
+      </c>
+      <c r="C4" s="5">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5">
+        <v>30</v>
+      </c>
+      <c r="E4" s="5">
+        <v>5</v>
+      </c>
+      <c r="F4" s="5">
+        <v>25</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>16</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>72</v>
+      </c>
+      <c r="C5" s="5">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>44</v>
+      </c>
+      <c r="C6" s="5">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <v>38</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>38</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>34</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>80</v>
+      </c>
+      <c r="C7" s="5">
+        <v>8</v>
+      </c>
+      <c r="D7" s="5">
+        <v>8</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>6</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>52</v>
+      </c>
+      <c r="C8" s="5">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5">
+        <v>22</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>22</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>8</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>50</v>
+      </c>
+      <c r="C9" s="5">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5">
+        <v>39</v>
+      </c>
+      <c r="E9" s="5">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5">
+        <v>32</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5">
+        <v>7</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>28</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>64</v>
+      </c>
+      <c r="C10" s="5">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>12</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>52</v>
+      </c>
+      <c r="C11" s="5">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5">
+        <v>29</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <v>28</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>20</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>52</v>
+      </c>
+      <c r="C12" s="5">
+        <v>22</v>
+      </c>
+      <c r="D12" s="5">
+        <v>22</v>
+      </c>
+      <c r="E12" s="5">
+        <v>4</v>
+      </c>
+      <c r="F12" s="5">
+        <v>18</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>4</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>12</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>56</v>
+      </c>
+      <c r="C13" s="5">
+        <v>20</v>
+      </c>
+      <c r="D13" s="5">
+        <v>20</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>20</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>12</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>83</v>
+      </c>
+      <c r="C14" s="5">
+        <v>7</v>
+      </c>
+      <c r="D14" s="5">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>6</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>4</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>78</v>
+      </c>
+      <c r="C15" s="5">
+        <v>12</v>
+      </c>
+      <c r="D15" s="5">
+        <v>6</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>6</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>2</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>34</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>58</v>
+      </c>
+      <c r="E16" s="5">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5">
+        <v>50</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>8</v>
+      </c>
+      <c r="I16" s="5">
+        <v>7</v>
+      </c>
+      <c r="J16" s="5">
+        <v>3</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>39</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>82</v>
+      </c>
+      <c r="C17" s="5">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5">
+        <v>6</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>6</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>4</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6864,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1917545807149104</v>
@@ -3960,10 +6923,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1865575586582199</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1178489327605477</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0922404620269217</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1811916126949029</v>
@@ -4001,10 +6982,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.004246569606556549</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1822532550965421</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08336841081661199</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5270097301308105</v>
@@ -4042,9 +7041,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4024920214503567</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6426775879633286</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2231676227192878</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7164,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2512092751052073</v>
@@ -4173,10 +7223,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2531359397813214</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1338409736519394</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0910166399400298</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2517747265449799</v>
@@ -4214,17 +7282,33 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1277104080606932</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2846507276850403</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1551210203071681</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>3.585140732023316</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>3.773754504415589</v>
       </c>
@@ -4255,9 +7339,27 @@
       <c r="M5" s="5">
         <v>8</v>
       </c>
+      <c r="N5" s="4">
+        <v>4.012845142307143</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5338468229863205</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1995608324218878</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7462,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1930189970792178</v>
@@ -4386,10 +7521,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1649182451239076</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1054757315821995</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09037573873912723</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1160630309023531</v>
@@ -4427,10 +7580,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.08853602042722304</v>
+      </c>
+      <c r="O4" s="5">
+        <v>26</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08957413500627298</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09110169712622114</v>
+      </c>
+      <c r="R4" s="5">
+        <v>26</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1445283129382666</v>
@@ -4468,9 +7639,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.004107811810706607</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1455552658909433</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0772767185844941</v>
+      </c>
+      <c r="R5" s="5">
+        <v>20</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7762,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2312844745806864</v>
@@ -4599,10 +7821,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2357255562365708</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2254758281909283</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1979343828828291</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2128587377023194</v>
@@ -4640,10 +7880,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1291477029876589</v>
+      </c>
+      <c r="O4" s="5">
+        <v>16</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1802618719213811</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2242473105688472</v>
+      </c>
+      <c r="R4" s="5">
+        <v>16</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6492699393193782</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4988120520953601</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8984254487500287</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2396928605371329</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8062,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.07332887449249981</v>
@@ -4812,10 +8121,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01809442795915856</v>
+      </c>
+      <c r="O3" s="5">
+        <v>30</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06654346400781534</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06542013884548699</v>
+      </c>
+      <c r="R3" s="5">
+        <v>30</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.09118145102523556</v>
@@ -4853,10 +8180,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.002197149158563759</v>
+      </c>
+      <c r="O4" s="5">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09145609467005604</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07219929035992681</v>
+      </c>
+      <c r="R4" s="5">
+        <v>28</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1616496496314959</v>
@@ -4894,9 +8239,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.06774791593138926</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1481779219580165</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07813141803978664</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1867457055972445</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1576969009362092</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.141375231288175</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.13010204081633</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.06711409395973</v>
-      </c>
-      <c r="G3" s="5">
-        <v>32</v>
-      </c>
-      <c r="H3" s="5">
-        <v>24</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>6</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>6</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1555590689175176</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1686865839760918</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1909914399592415</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.40688775510205</v>
-      </c>
-      <c r="F4" s="4">
-        <v>72.47273489932886</v>
-      </c>
-      <c r="G4" s="5">
-        <v>32</v>
-      </c>
-      <c r="H4" s="5">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5">
-        <v>6</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>6</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3201759959009612</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3866626022643647</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5109692009049227</v>
-      </c>
-      <c r="E5" s="4">
-        <v>78.67028061224489</v>
-      </c>
-      <c r="F5" s="4">
-        <v>53.89890939597316</v>
-      </c>
-      <c r="G5" s="5">
-        <v>32</v>
-      </c>
-      <c r="H5" s="5">
-        <v>8</v>
-      </c>
-      <c r="I5" s="5">
-        <v>14</v>
-      </c>
-      <c r="J5" s="5">
-        <v>10</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>10</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.9036444197497424</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.9812959807993231</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.9136791258381542</v>
-      </c>
-      <c r="E3" s="4">
-        <v>75.84396258503402</v>
-      </c>
-      <c r="F3" s="4">
-        <v>75.22930648769581</v>
-      </c>
-      <c r="G3" s="5">
-        <v>32</v>
-      </c>
-      <c r="H3" s="5">
-        <v>22</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>10</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>10</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4847837444817884</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5408934887449789</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4863735195672376</v>
-      </c>
-      <c r="E4" s="4">
-        <v>76.50403911564662</v>
-      </c>
-      <c r="F4" s="4">
-        <v>72.51503076062546</v>
-      </c>
-      <c r="G4" s="5">
-        <v>32</v>
-      </c>
-      <c r="H4" s="5">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>12</v>
-      </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5">
-        <v>10</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.9334257724267836</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.9909065687482013</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.8087549478741458</v>
-      </c>
-      <c r="E5" s="4">
-        <v>65.35182823129239</v>
-      </c>
-      <c r="F5" s="4">
-        <v>55.46071029082763</v>
-      </c>
-      <c r="G5" s="5">
-        <v>32</v>
-      </c>
-      <c r="H5" s="5">
-        <v>8</v>
-      </c>
-      <c r="I5" s="5">
-        <v>7</v>
-      </c>
-      <c r="J5" s="5">
-        <v>17</v>
-      </c>
-      <c r="K5" s="5">
-        <v>5</v>
-      </c>
-      <c r="L5" s="5">
-        <v>12</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/FloresActive2020.xlsx
+++ b/public/downloads/FloresActive2020.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1084329173742126</v>
+        <v>0.03695920820658216</v>
       </c>
       <c r="O3" s="5">
         <v>24</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1873842471907199</v>
+        <v>0.1795196445974868</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.163449317763046</v>
+        <v>0.1529631809720685</v>
       </c>
       <c r="R3" s="5">
         <v>24</v>
@@ -1616,13 +1616,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1139907354166388</v>
+        <v>0.1550614015980241</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1358347447442895</v>
+        <v>0.1409685780169626</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1313027635058236</v>
@@ -1675,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3866626022643647</v>
+        <v>0.3956301310058077</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.422702074002875</v>
+        <v>0.4294277205589573</v>
       </c>
       <c r="Q5" s="4">
         <v>0.189695373273117</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9812959807993231</v>
+        <v>0.9710520369640676</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2397215958098913</v>
+        <v>0.2371606098510775</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1998112677208215</v>
+        <v>0.1988800000994347</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5408934887449789</v>
+        <v>0.5203767839910824</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2083847138374097</v>
+        <v>0.2044602718920956</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2228164212460968</v>
+        <v>0.2228164212460967</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.9909065687482013</v>
+        <v>1.0102297119318</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>1.263456585764194</v>
+        <v>1.275673700722695</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09053968377930488</v>
+        <v>0.08143871406251435</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01823851120300507</v>
+        <v>0.07067097887458784</v>
       </c>
       <c r="O3" s="5">
         <v>30</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1432850208500692</v>
+        <v>0.1333417282901367</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.13459914897243</v>
+        <v>0.1180656709033291</v>
       </c>
       <c r="R3" s="5">
         <v>30</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01718687351574845</v>
+        <v>-0.003530827607457043</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1234749091836523</v>
+        <v>0.1240534459241501</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09001253007301536</v>
+        <v>0.08623189709091522</v>
       </c>
       <c r="R4" s="5">
         <v>24</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1453087527798594</v>
+        <v>0.1618192545255539</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3650256626391886</v>
+        <v>0.3732814772078361</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09409969255448772</v>
+        <v>0.09079939603190965</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1361825174318221</v>
+        <v>0.1790969422095259</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.179968819332004</v>
+        <v>0.185333122429217</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1496413203134285</v>
+        <v>0.1463402107151436</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -2516,13 +2516,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02073810971091916</v>
+        <v>0.009748461953080323</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1226358898784241</v>
+        <v>0.1212621839086943</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1028032739687546</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4580083439673217</v>
+        <v>0.4014153545141994</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8034131196704486</v>
+        <v>0.7538942538989666</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08051013341147002</v>
+        <v>0.06164580359376259</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.006114199231869104</v>
+        <v>0.0803918767114169</v>
       </c>
       <c r="O3" s="5">
         <v>27</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1534297400397844</v>
+        <v>0.1517750299365268</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1282384131149184</v>
+        <v>0.1166654889988405</v>
       </c>
       <c r="R3" s="5">
         <v>27</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.09143967352438147</v>
+        <v>-0.08856158237307454</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08712304540424848</v>
+        <v>0.08766268749511852</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06352271159842908</v>
+        <v>0.06337123311678133</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.07680233613528269</v>
+        <v>0.1237793424243705</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5539653596850881</v>
+        <v>0.5862706345776836</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06975680611979997</v>
+        <v>0.05414358039062487</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04745056970985546</v>
+        <v>-0.02757677067137365</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1026831647686435</v>
+        <v>0.1051673896484537</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08379655321330427</v>
+        <v>0.08226779944111338</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2063922611655414</v>
+        <v>-0.1874594769116413</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1342232975488358</v>
+        <v>0.134871792055673</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08784778205000976</v>
+        <v>0.08509881641016932</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.03691797655172877</v>
+        <v>-0.025104410825179</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4509789854492503</v>
+        <v>0.4583624640283439</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04403327346563402</v>
+        <v>0.04167056032032405</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3729601556301379</v>
+        <v>0.3880094104333254</v>
       </c>
       <c r="O3" s="5">
         <v>30</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07972252781469347</v>
+        <v>0.07972254271586257</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08133720671493162</v>
+        <v>0.08033393895596617</v>
       </c>
       <c r="R3" s="5">
         <v>30</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1789393367317205</v>
+        <v>0.1836303473277496</v>
       </c>
       <c r="O4" s="5">
         <v>28</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05820572572333539</v>
+        <v>0.05798502220390354</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05261639683380094</v>
+        <v>0.05236416424016455</v>
       </c>
       <c r="R4" s="5">
         <v>28</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3063374167557849</v>
+        <v>0.3325330172008396</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1434354921257837</v>
+        <v>0.13864384122566</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06381629813735254</v>
+        <v>0.05594482474001523</v>
       </c>
       <c r="R5" s="5">
         <v>25</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2274285967907106</v>
+        <v>-0.2216669880237614</v>
       </c>
       <c r="O3" s="5">
         <v>30</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07942627253031928</v>
+        <v>0.07870607329709811</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06847086835199741</v>
+        <v>0.06808676308769143</v>
       </c>
       <c r="R3" s="5">
         <v>30</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3463653981747571</v>
+        <v>-0.3307496177928044</v>
       </c>
       <c r="O4" s="5">
         <v>28</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1069591392740156</v>
+        <v>0.1037949801440596</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06072372010026771</v>
+        <v>0.05710753823746094</v>
       </c>
       <c r="R4" s="5">
         <v>28</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4983092251751334</v>
+        <v>-0.4681929666716371</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1607667576311123</v>
+        <v>0.1624594628838043</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0982460521811285</v>
+        <v>0.09308935475774227</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5787497327404897</v>
+        <v>0.5866558894606286</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5542227504002055</v>
+        <v>0.5514690117187142</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4147755202636663</v>
+        <v>0.4147755277142474</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05900197025465533</v>
+        <v>0.05860859604434204</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6809700602118953</v>
+        <v>0.6699707811357687</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1388296321789266</v>
+        <v>-0.1635507697602261</v>
       </c>
       <c r="O3" s="5">
         <v>30</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07306235924582898</v>
+        <v>0.06550169009991946</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0697167127062592</v>
+        <v>0.06330007478937567</v>
       </c>
       <c r="R3" s="5">
         <v>30</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2097424409488105</v>
+        <v>-0.2164470020113658</v>
       </c>
       <c r="O4" s="5">
         <v>28</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1059114007419001</v>
+        <v>0.1048312115295815</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07198987345077534</v>
+        <v>0.07171316593134769</v>
       </c>
       <c r="R4" s="5">
         <v>28</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.235324439839441</v>
+        <v>-0.2237249707034152</v>
       </c>
       <c r="O5" s="5">
         <v>24</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1312519382474235</v>
+        <v>0.1315214203981823</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.095378792456584</v>
+        <v>0.09380485713492466</v>
       </c>
       <c r="R5" s="5">
         <v>24</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3142599252734728</v>
+        <v>0.3189869500204867</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1101761418747389</v>
+        <v>0.1093905193693083</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1458403697112343</v>
+        <v>0.145400170591446</v>
       </c>
       <c r="K3" s="4">
         <v>73.04315476190501</v>
@@ -4571,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3174461747744334</v>
+        <v>0.3196555625292691</v>
       </c>
       <c r="I4" s="4">
-        <v>0.133146481324683</v>
+        <v>0.1279798437445336</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2385444603736701</v>
+        <v>0.2424480999536792</v>
       </c>
       <c r="K4" s="4">
         <v>81.85515873015865</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1135350441598052</v>
+        <v>0.1120136119310378</v>
       </c>
       <c r="I5" s="4">
-        <v>0.08699927366929083</v>
+        <v>0.08483438519595173</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1229860506044749</v>
+        <v>0.1255833409678525</v>
       </c>
       <c r="K5" s="4">
         <v>85.26856575963723</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4347210496207794</v>
+        <v>0.4461422224633924</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2150951707058</v>
+        <v>0.2094724490465322</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2683755726456744</v>
+        <v>0.2946223232548799</v>
       </c>
       <c r="K6" s="4">
         <v>69.90610827664401</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1020591602119626</v>
+        <v>0.1011364877368131</v>
       </c>
       <c r="I7" s="4">
-        <v>0.07128844365397333</v>
+        <v>0.06820115652246272</v>
       </c>
       <c r="J7" s="4">
-        <v>0.07299705688779545</v>
+        <v>0.07307664277181065</v>
       </c>
       <c r="K7" s="4">
         <v>92.96343537414968</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2486403553126282</v>
+        <v>0.2499719810578022</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1551231131272022</v>
+        <v>0.1502833576852125</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1737207949261137</v>
+        <v>0.1645765715056992</v>
       </c>
       <c r="K8" s="4">
         <v>83.40242346938747</v>
@@ -4821,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.570520965137165</v>
+        <v>0.5724315274886228</v>
       </c>
       <c r="I9" s="4">
-        <v>0.191529875700289</v>
+        <v>0.1896639627921922</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2239449648504734</v>
+        <v>0.2291925354840198</v>
       </c>
       <c r="K9" s="4">
         <v>72.56660997732412</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2105951975576367</v>
+        <v>0.210225550474041</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1115511268198461</v>
+        <v>0.1018676502750146</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1148728350544145</v>
+        <v>0.1183002593778945</v>
       </c>
       <c r="K10" s="4">
         <v>86.79209183673511</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.368672609626959</v>
+        <v>0.3534965200789593</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1236500116921741</v>
+        <v>0.119822803452527</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1683231453380716</v>
+        <v>0.1629854479246688</v>
       </c>
       <c r="K11" s="4">
         <v>81.95188492063491</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.264839381709707</v>
+        <v>0.275236117336443</v>
       </c>
       <c r="I12" s="4">
-        <v>0.09784441367676439</v>
+        <v>0.089978521433294</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1185811307631417</v>
+        <v>0.1293409682132136</v>
       </c>
       <c r="K12" s="4">
         <v>86.84063208616764</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.2292951492555766</v>
+        <v>0.2328005485774902</v>
       </c>
       <c r="I13" s="4">
-        <v>0.07814283498575796</v>
+        <v>0.0760293699442067</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1108401261971524</v>
+        <v>0.1162856157567778</v>
       </c>
       <c r="K13" s="4">
         <v>86.23086734693865</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.09378791522127085</v>
+        <v>0.0921171353818087</v>
       </c>
       <c r="I14" s="4">
-        <v>0.06637087670154446</v>
+        <v>0.06355223356510811</v>
       </c>
       <c r="J14" s="4">
-        <v>0.07923886178575115</v>
+        <v>0.07470917230513352</v>
       </c>
       <c r="K14" s="4">
         <v>80.41206065759638</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1157173898118157</v>
+        <v>0.1149868387749873</v>
       </c>
       <c r="I15" s="4">
-        <v>0.07332450329474344</v>
+        <v>0.07055642382608326</v>
       </c>
       <c r="J15" s="4">
-        <v>0.07696705991267039</v>
+        <v>0.07740223694859705</v>
       </c>
       <c r="K15" s="4">
         <v>94.20705782312923</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.4076491903244928</v>
+        <v>0.4076491928080198</v>
       </c>
       <c r="I16" s="4">
-        <v>0.05063722821628335</v>
+        <v>0.05047525060027199</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1411355123080472</v>
+        <v>0.1432566492539577</v>
       </c>
       <c r="K16" s="4">
         <v>59.80831916099748</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1034085660783842</v>
+        <v>0.1006181073425611</v>
       </c>
       <c r="I17" s="4">
-        <v>0.07800376654594514</v>
+        <v>0.0751010665975268</v>
       </c>
       <c r="J17" s="4">
-        <v>0.08507786156237755</v>
+        <v>0.08246828664822629</v>
       </c>
       <c r="K17" s="4">
         <v>92.00538548752832</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1865575586582199</v>
+        <v>0.1820345387829434</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1178489327605477</v>
+        <v>0.1167181777917286</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0922404620269217</v>
+        <v>0.09182927840189657</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -6983,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.004246569606556549</v>
+        <v>0.01469391283870891</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1822532550965421</v>
+        <v>0.1849242336133585</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08336841081661199</v>
+        <v>0.08181843907895152</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -7042,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4024920214503567</v>
+        <v>0.4227173825592274</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6426775879633286</v>
+        <v>0.6553184386563728</v>
       </c>
       <c r="Q5" s="4">
         <v>0.2231676227192878</v>
@@ -7224,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2531359397813214</v>
+        <v>0.3079758946685729</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1338409736519394</v>
+        <v>0.1406959829140071</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0910166399400298</v>
+        <v>0.08603121117015049</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1277104080606932</v>
+        <v>0.1864087560464327</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2846507276850403</v>
+        <v>0.3066626454325956</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1551210203071681</v>
+        <v>0.148599047869469</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -7340,16 +7340,16 @@
         <v>8</v>
       </c>
       <c r="N5" s="4">
-        <v>4.012845142307143</v>
+        <v>3.963508229963395</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5338468229863205</v>
+        <v>0.5116080592412047</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1995608324218878</v>
+        <v>0.1969453740429827</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -7522,16 +7522,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1649182451239076</v>
+        <v>-0.115981662383092</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1054757315821995</v>
+        <v>0.1076482093810007</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09037573873912723</v>
+        <v>0.0866115054298925</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -7581,16 +7581,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08853602042722304</v>
+        <v>-0.07131716304286329</v>
       </c>
       <c r="O4" s="5">
         <v>26</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08957413500627298</v>
+        <v>0.08883775409153571</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09110169712622114</v>
+        <v>0.0888708546631322</v>
       </c>
       <c r="R4" s="5">
         <v>26</v>
@@ -7640,16 +7640,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.004107811810706607</v>
+        <v>-0.02229238681218249</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1455552658909433</v>
+        <v>0.1395548723205771</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0772767185844941</v>
+        <v>0.07727671858449411</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -7822,13 +7822,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2357255562365708</v>
+        <v>0.1676295456897208</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2254758281909283</v>
+        <v>0.216963826872572</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1979343828828291</v>
@@ -7881,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1291477029876589</v>
+        <v>0.05926664422790395</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1802618719213811</v>
+        <v>0.187606686906733</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2242473105688472</v>
+        <v>0.2087848260058607</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -7940,13 +7940,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4988120520953601</v>
+        <v>0.5460529919098178</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8984254487500287</v>
+        <v>0.933856153610872</v>
       </c>
       <c r="Q5" s="4">
         <v>0.2396928605371329</v>
@@ -8122,16 +8122,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01809442795915856</v>
+        <v>-0.04150293182374298</v>
       </c>
       <c r="O3" s="5">
         <v>30</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06654346400781534</v>
+        <v>0.06120501887695795</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06542013884548699</v>
+        <v>0.06128636429687807</v>
       </c>
       <c r="R3" s="5">
         <v>30</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.002197149158563759</v>
+        <v>0.009713664083250251</v>
       </c>
       <c r="O4" s="5">
         <v>28</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09145609467005604</v>
+        <v>0.09239565903564184</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07219929035992681</v>
+        <v>0.0721992903599268</v>
       </c>
       <c r="R4" s="5">
         <v>28</v>
@@ -8240,16 +8240,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.06774791593138926</v>
+        <v>0.1011914982750568</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1481779219580165</v>
+        <v>0.1498087852978394</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07813141803978664</v>
+        <v>0.0725418846733057</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
